--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CORREIA DENTADA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CORREIA DENTADA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -482,7 +482,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -490,22 +494,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0751320982063</t>
+          <t>0602883766242</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CORREIA DENTADA IRON NEO115 179304</t>
+          <t>CORREIA DENTADA IRON PCX150 179305</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>190</t>
         </is>
       </c>
     </row>
@@ -515,20 +519,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0751320982056</t>
+          <t>0602883766273</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CORREIA DENTADA IRON LEAD110 179303</t>
+          <t>CORREIA DENTADA IRON ELITE125 187998</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -536,20 +544,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0602883766242</t>
+          <t>0618341654952</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CORREIA DENTADA IRON PCX150 179305</t>
+          <t>CORREIA DENTADA IRON PCX150 2016 A 2018 201574</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -557,12 +569,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0602883766273</t>
+          <t>0502883766259</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CORREIA DENTADA IRON ELITE125 187998</t>
+          <t>CORREIDA DENTADA IRON NMAX160 TODAS VERSÕES/ GPD150 2015 A 2018 187993</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -572,7 +584,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>110</t>
         </is>
       </c>
     </row>
@@ -582,12 +594,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0618341654952</t>
+          <t>7909201083511</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CORREIA DENTADA IRON PCX150 2016 A 2018 201574</t>
+          <t>CORREIA DENTADA GP PCX150 2019</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -595,7 +607,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -603,12 +619,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0502883766259</t>
+          <t>7909201083528</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CORREIDA DENTADA IRON NMAX160 TODAS VERSÕES/ GPD150 2015 A 2018 187993</t>
+          <t>CORREIA DENTADA GP PCX160 2023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -618,7 +634,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>190</t>
         </is>
       </c>
     </row>
@@ -628,22 +644,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7909201083511</t>
+          <t>7909201000419</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CORREIA DENTADA GP PCX150 2019</t>
+          <t>CORREIA DENTADA GP PCX150 214 A 2015</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>110</t>
         </is>
       </c>
     </row>
@@ -653,17 +669,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7909201083528</t>
+          <t>7909201051015</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CORREIA DENTADA GP PCX160 2023</t>
+          <t>CORREIA DENTADA GP PCX150 2016 A 2018 1101981</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -678,22 +694,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7909201000419</t>
+          <t>7908305615802</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CORREIA DENTADA GP PCX150 214 A 2015</t>
+          <t>CORREIA DENTADA MHX NMAX160 2017 A 2020</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -703,20 +719,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7909201051015</t>
+          <t>7899468055560</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CORREIA DENTADA GP PCX150 2016 A 2018 1101981</t>
+          <t>CORREIA DENTADA MHX BURGMAN125 2011 A 2016</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -724,12 +744,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7908305615802</t>
+          <t>7899468069703</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CORREIA DENTADA MHX NMAX160 2017 A 2020</t>
+          <t>CORREIA DENTADA MHX LEAD110 2010 A 2013/ BURGMAN125 2010</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -738,56 +758,6 @@
         </is>
       </c>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>7899468055560</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CORREIA DENTADA MHX BURGMAN125 2011 A 2016</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>7899468069703</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CORREIA DENTADA MHX LEAD110 2010 A 2013/ BURGMAN125 2010</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
         <is>
           <t>80</t>
         </is>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CORREIA DENTADA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CORREIA DENTADA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,11 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -732,11 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -755,11 +690,6 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
     </row>
